--- a/pepline/result/deconv6+_result.xlsx
+++ b/pepline/result/deconv6+_result.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="8960" yWindow="760" windowWidth="38200" windowHeight="24940" tabRatio="600" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="8960" yWindow="760" windowWidth="38200" windowHeight="24940" tabRatio="600" firstSheet="0" activeTab="8" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,6 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YPS6+_non_deconv" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YPS6+_decov" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KWK6+_test2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KWK6+_test3" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KWK6+_test4" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -562,6 +564,2360 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>N=1000</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>All Coverage=27.0%</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>isocolumn:0</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>parent(0.002388)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>1(0.001692)</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>2(0.001986)</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>3(0.001452)</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>4(0.001570)</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>isocolumn:-260.1</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>-260.1(0.001784)</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>-259.097(0.002471)</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>isocolumn:-162.04</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>-162.04(0.000454)</t>
+        </is>
+      </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>-161.039(0.001340)</t>
+        </is>
+      </c>
+      <c r="P1" s="5" t="inlineStr">
+        <is>
+          <t>isocolumn:-16.002</t>
+        </is>
+      </c>
+      <c r="Q1" s="5" t="inlineStr">
+        <is>
+          <t>-16.002(0.000900)</t>
+        </is>
+      </c>
+      <c r="R1" s="5" t="inlineStr">
+        <is>
+          <t>-14.997(0.006422)</t>
+        </is>
+      </c>
+      <c r="S1" s="5" t="inlineStr">
+        <is>
+          <t>Row Count</t>
+        </is>
+      </c>
+      <c r="T1" s="5" t="inlineStr">
+        <is>
+          <t>theoretical mass</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>b1, y36</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>(129.102, 3874.29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>b2, y35</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>(315.182, 3688.211)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>b3, y34</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>(443.276, 3560.116)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>b4, y33</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>(556.361, 3447.032)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>b5, y32</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>(703.429, 3299.964)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>b6, y31</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>(831.524, 3171.869)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>b7, y30</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>(959.619, 3043.774)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>b8, y29</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>(1072.703, 2930.69)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>b9, y28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>(1201.746, 2801.647)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>b10, y27</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>(1329.84, 2673.552)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>b11, y26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>(1428.909, 2574.484)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>b12, y25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>(1485.93, 2517.462)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>b13, y24</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>(1613.989, 2389.404)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>b14, y23</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>(1728.032, 2275.361)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>b15, y22</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>(1841.116, 2162.277)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>b16, y21</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>(1997.217, 2006.176)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>b17, y20</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>(2112.244, 1891.149)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>b18, y19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>(2169.265, 1834.127)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>b19, y18</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>(2282.349, 1721.043)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>b20, y17</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>(2395.434, 1607.959)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>b21, y16</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>(2523.529, 1479.864)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>b22, y15</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>(2594.566, 1408.827)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>b23, y14</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>(2651.587, 1351.806)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>b24, y13</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>(2748.64, 1254.753)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>b25, y12</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>(2819.677, 1183.716)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>b26, y11</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0, 0, [4.0, 2.0], (0.008, 0.003), [44]</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>(2918.745, 1084.647)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>b27, y10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0, 0, [4.0, 2.0], (0.007, 0.003), [87]</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>(2989.782, 1013.61)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>b28, y9</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0, 0, [4.0, 2.0], (0.007, 0.002), [72]</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>(3088.851, 914.542)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>b29, y8</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0, 0, [4.0, 2.0], (0.008, 0.002), [21]</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>(3187.919, 815.473)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>b30, y7</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0, 0, [4.0, 2.0], (0.008, 0.002), [5]</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>(3244.941, 758.452)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>b31, y6</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0, 0, [4.0, 2.0], (0.009, 0.001), [16]</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>(3372.999, 630.393)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>b32, y5</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0, 0, [4.0, 2.0], (0.01, 0.001), [3]</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>(3444.036, 559.356)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>b33, y4</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0, 0, [5.0, 1.0], (0.008, 0.002), [12]</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>(3545.084, 458.309)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>b34, y3</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>(3673.143, 330.25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>b35, y2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0, 0, [5.0, 1.0], (0.008, 0.001), [41]</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>(3786.227, 217.166)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>b36, y1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>(3857.264, 146.129)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Col Count</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>9</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>36</v>
+      </c>
+      <c r="T38" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>FFC</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>72</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="n">
+        <v>6</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>FPR0</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="n">
+        <v>6</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>FPR1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>offset</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>FPR0_LIST_1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>(280.18258, 745.84842, [1.0, 5.0], 165.0)</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>(559.35828, 689.6149800000001, [3.0, 3.0], 20.0)</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>FPR0_LIST_2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>(559.35828, 689.6149800000001, [3.0, 3.0], 28.0)</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>FPR0_LIST_3</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>(559.35828, 689.6149800000001, [3.0, 3.0], 47.0)</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>TFPR0_LIST_1</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>(280.1826, 3729.2421, 4009.4247)</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>(1678.0748, 2068.8449, 3746.9198)</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>TFPR0_LIST_2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>(1678.0748, 2068.8449, 3746.9198)</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>TFPR0_LIST_3</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>(1678.0748, 2068.8449, 3746.9198)</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>FPR1_LIST_1</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>FPR1_LIST_2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>FPR1_LIST_3</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>TFPR1_LIST_1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>TFPR1_LIST_2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>TFPR1_LIST_3</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Modifications_Count</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>|SIM(A*,B)|</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>9</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>|DIFF(A*,B)|</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -10015,77 +12371,77 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M57"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>N=2000</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>All Coverage=27.0%</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>isocolumn:0</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>parent(0.02)</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>1(0.05)</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>2(0.03)</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>3(0.04)</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>4(0.06)</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>5(0.03)</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>6(0.04)</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Row Count</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>theoretical mass</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>b1, y36</t>
         </is>
@@ -10100,14 +12456,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
         <v>0</v>
       </c>
@@ -10118,7 +12466,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>b2, y35</t>
         </is>
@@ -10133,14 +12481,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
         <v>0</v>
       </c>
@@ -10151,7 +12491,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>b3, y34</t>
         </is>
@@ -10166,14 +12506,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>0</v>
       </c>
@@ -10184,7 +12516,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>b4, y33</t>
         </is>
@@ -10199,14 +12531,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
         <v>0</v>
       </c>
@@ -10217,7 +12541,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>b5, y32</t>
         </is>
@@ -10232,14 +12556,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>0</v>
       </c>
@@ -10250,7 +12566,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>b6, y31</t>
         </is>
@@ -10265,14 +12581,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
         <v>0</v>
       </c>
@@ -10283,7 +12591,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>b7, y30</t>
         </is>
@@ -10298,14 +12606,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>0</v>
       </c>
@@ -10316,7 +12616,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>b8, y29</t>
         </is>
@@ -10331,14 +12631,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>0</v>
       </c>
@@ -10349,7 +12641,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>b9, y28</t>
         </is>
@@ -10364,14 +12656,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>0</v>
       </c>
@@ -10382,7 +12666,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>b10, y27</t>
         </is>
@@ -10397,14 +12681,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>0</v>
       </c>
@@ -10415,7 +12691,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>b11, y26</t>
         </is>
@@ -10430,14 +12706,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
         <v>0</v>
       </c>
@@ -10448,7 +12716,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>b12, y25</t>
         </is>
@@ -10463,14 +12731,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
         <v>0</v>
       </c>
@@ -10481,7 +12741,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>b13, y24</t>
         </is>
@@ -10496,14 +12756,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
         <v>0</v>
       </c>
@@ -10514,7 +12766,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>b14, y23</t>
         </is>
@@ -10529,14 +12781,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
         <v>0</v>
       </c>
@@ -10547,7 +12791,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>b15, y22</t>
         </is>
@@ -10562,14 +12806,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
         <v>0</v>
       </c>
@@ -10580,7 +12816,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>b16, y21</t>
         </is>
@@ -10595,14 +12831,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
         <v>0</v>
       </c>
@@ -10613,7 +12841,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>b17, y20</t>
         </is>
@@ -10628,14 +12856,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
         <v>0</v>
       </c>
@@ -10646,7 +12866,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>b18, y19</t>
         </is>
@@ -10661,14 +12881,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
         <v>0</v>
       </c>
@@ -10679,7 +12891,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>b19, y18</t>
         </is>
@@ -10694,14 +12906,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
         <v>0</v>
       </c>
@@ -10712,7 +12916,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>b20, y17</t>
         </is>
@@ -10727,14 +12931,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
         <v>0</v>
       </c>
@@ -10745,7 +12941,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>b21, y16</t>
         </is>
@@ -10765,17 +12961,11 @@
           <t>(2, 0)</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>+2, 0, [4.0, 2.0], (0.005, 0.018), [1228]</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
         <v>1</v>
       </c>
@@ -10786,7 +12976,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>b22, y15</t>
         </is>
@@ -10801,14 +12991,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
         <v>0</v>
       </c>
@@ -10819,7 +13001,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>b23, y14</t>
         </is>
@@ -10834,14 +13016,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
         <v>0</v>
       </c>
@@ -10852,7 +13026,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>b24, y13</t>
         </is>
@@ -10867,14 +13041,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
         <v>0</v>
       </c>
@@ -10885,7 +13051,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>b25, y12</t>
         </is>
@@ -10900,14 +13066,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
         <v>0</v>
       </c>
@@ -10918,7 +13076,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>b26, y11</t>
         </is>
@@ -10943,12 +13101,6 @@
           <t>0, 0, [4.0, 2.0], (0.008, 0.009), [44]</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
         <v>1</v>
       </c>
@@ -10959,7 +13111,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>b27, y10</t>
         </is>
@@ -10984,12 +13136,6 @@
           <t>0, 0, [4.0, 2.0], (0.007, 0.003), [87]</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
         <v>1</v>
       </c>
@@ -11000,7 +13146,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>b28, y9</t>
         </is>
@@ -11025,12 +13171,6 @@
           <t>0, 0, [4.0, 2.0], (0.007, 0.002), [72]</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
         <v>1</v>
       </c>
@@ -11041,7 +13181,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>b29, y8</t>
         </is>
@@ -11066,12 +13206,6 @@
           <t>0, 0, [4.0, 2.0], (0.008, 0.002), [21]</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
         <v>1</v>
       </c>
@@ -11082,7 +13216,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>b30, y7</t>
         </is>
@@ -11107,12 +13241,6 @@
           <t>0, 0, [4.0, 2.0], (0.008, 0.002), [5]</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
         <v>1</v>
       </c>
@@ -11123,7 +13251,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>b31, y6</t>
         </is>
@@ -11153,11 +13281,6 @@
           <t>0, +1, [5.0, 1.0], (0.006, 0.002), [972]</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
         <v>2</v>
       </c>
@@ -11168,7 +13291,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>b32, y5</t>
         </is>
@@ -11193,12 +13316,6 @@
           <t>0, 0, [4.0, 2.0], (0.01, 0.001), [3]</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
         <v>1</v>
       </c>
@@ -11209,7 +13326,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>b33, y4</t>
         </is>
@@ -11234,12 +13351,6 @@
           <t>0, 0, [5.0, 1.0], (0.008, 0.002), [12]</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
         <v>1</v>
       </c>
@@ -11250,7 +13361,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>b34, y3</t>
         </is>
@@ -11265,14 +13376,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
         <v>0</v>
       </c>
@@ -11283,7 +13386,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>b35, y2</t>
         </is>
@@ -11298,14 +13401,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
         <v>0</v>
       </c>
@@ -11316,7 +13411,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>b36, y1</t>
         </is>
@@ -11331,14 +13426,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
         <v>0</v>
       </c>
@@ -11349,7 +13436,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Col Count</t>
         </is>
@@ -11364,7 +13451,6 @@
           <t>+</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
         <v>8</v>
       </c>
@@ -11394,14 +13480,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>FFC</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
         <v>82</v>
       </c>
@@ -11423,18 +13506,13 @@
       <c r="K39" t="n">
         <v>0</v>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>FPR0</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
         <v>0</v>
       </c>
@@ -11456,18 +13534,13 @@
       <c r="K40" t="n">
         <v>0</v>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>FPR1</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
         <v>0</v>
       </c>
@@ -11489,38 +13562,20 @@
       <c r="K41" t="n">
         <v>0</v>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>offset</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>FPR0_LIST_1</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>(271.17728, 866.526655, [2.0, 4.0], 1460.0)</t>
@@ -11531,69 +13586,37 @@
           <t>(280.18258, 745.84842, [1.0, 5.0], 165.0)</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>(624.78386, 887.53088, [5.0, 1.0], 1588.0)</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>FPR0_LIST_2</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>(663.65182, 690.2167800000001, [5.0, 1.0], 1886.0)</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>FPR0_LIST_3</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>TFPR0_LIST_1</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>(542.3546, 3466.1066, 4008.4612)</t>
@@ -11604,183 +13627,85 @@
           <t>(280.1826, 3729.2421, 4009.4247)</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>(3123.9193, 887.5309, 4011.4502)</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>TFPR0_LIST_2</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>(3318.2591, 690.2168, 4008.4759)</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>TFPR0_LIST_3</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>FPR1_LIST_1</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>???, +4, [1.0, 5.0], ('n/a', 0.006), [1842]|</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>FPR1_LIST_2</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>FPR1_LIST_3</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>TFPR1_LIST_1</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>(442.287, 3568.1551, 4010.4421)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>TFPR1_LIST_2</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>TFPR1_LIST_3</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Modifications_Count</t>
         </is>
@@ -11791,7 +13716,6 @@
       <c r="C55" t="n">
         <v>0</v>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
         <v>0</v>
       </c>
@@ -11821,14 +13745,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>|SIM(A*,B)|</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
         <v>8</v>
       </c>
@@ -11850,18 +13771,13 @@
       <c r="K56" t="n">
         <v>0</v>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>|DIFF(A*,B)|</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
         <v>0</v>
       </c>
@@ -11883,8 +13799,1541 @@
       <c r="K57" t="n">
         <v>0</v>
       </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T57"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="32.83203125" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>N=1000</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>All Coverage=24.3%</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>isocolumn:0</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>parent(0.002388)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>1(0.001692)</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>2(0.001986)</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>3(0.001452)</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>4(0.001570)</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>isocolumn:-260.1</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>-260.1(0.001784)</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>-259.097(0.002471)</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>isocolumn:-162.04</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>-162.04(0.000454)</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>-161.039(0.001340)</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>isocolumn:-16.002</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>-16.002(0.000900)</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>-14.997(0.006422)</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Row Count</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>theoretical mass</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>b1, y36</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>(129.102, 3874.29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>b2, y35</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>(315.182, 3688.211)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>b3, y34</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>(443.276, 3560.116)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>b4, y33</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>(556.361, 3447.032)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>b5, y32</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>(703.429, 3299.964)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>b6, y31</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>(831.524, 3171.869)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>b7, y30</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>(959.619, 3043.774)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>b8, y29</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>(1072.703, 2930.69)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>b9, y28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>(1201.746, 2801.647)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>b10, y27</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>(1329.84, 2673.552)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>b11, y26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>(1428.909, 2574.484)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>b12, y25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>(1485.93, 2517.462)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>b13, y24</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>(1613.989, 2389.404)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>b14, y23</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>(1728.032, 2275.361)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>b15, y22</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>(1841.116, 2162.277)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>b16, y21</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>(1997.217, 2006.176)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>b17, y20</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>(2112.244, 1891.149)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>b18, y19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>(2169.265, 1834.127)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>b19, y18</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>(2282.349, 1721.043)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>b20, y17</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>(2395.434, 1607.959)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>b21, y16</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>(2523.529, 1479.864)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>b22, y15</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>(2594.566, 1408.827)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>b23, y14</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>(2651.587, 1351.806)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>b24, y13</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>(2748.64, 1254.753)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>b25, y12</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>(2819.677, 1183.716)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>b26, y11</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>(2918.745, 1084.647)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>b27, y10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0, 0, [4.0, 2.0], (0.007, 0.003), [87]</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>(2989.782, 1013.61)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>b28, y9</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0, 0, [4.0, 2.0], (0.007, 0.002), [72]</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>(3088.851, 914.542)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>b29, y8</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0, 0, [4.0, 2.0], (0.008, 0.002), [21]</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>(3187.919, 815.473)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>b30, y7</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0, 0, [4.0, 2.0], (0.008, 0.002), [5]</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>(3244.941, 758.452)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>b31, y6</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0, 0, [4.0, 2.0], (0.009, 0.001), [16]</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>(3372.999, 630.393)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>b32, y5</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0, 0, [4.0, 2.0], (0.01, 0.001), [3]</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>(3444.036, 559.356)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>b33, y4</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0, 0, [5.0, 1.0], (0.008, 0.002), [12]</t>
+        </is>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>(3545.084, 458.309)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>b34, y3</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>(3673.143, 330.25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>b35, y2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0, 0, [5.0, 1.0], (0.008, 0.001), [41]</t>
+        </is>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>(3786.227, 217.166)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>b36, y1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>(3857.264, 146.129)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Col Count</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>8</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>36</v>
+      </c>
+      <c r="T38" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>FFC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>68</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>6</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>FPR0</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>6</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>FPR1</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>offset</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>FPR0_LIST_1</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>(280.18258, 745.44708, [1.0, 5.0], 165.0)</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>(559.35828, 689.6149800000001, [3.0, 3.0], 20.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>FPR0_LIST_2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>(559.35828, 689.6149800000001, [3.0, 3.0], 28.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>FPR0_LIST_3</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>(559.35828, 689.6149800000001, [3.0, 3.0], 47.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>TFPR0_LIST_1</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>(280.1826, 3727.2354, 4007.418)</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>(1678.0748, 2068.8449, 3746.9198)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>TFPR0_LIST_2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>(1678.0748, 2068.8449, 3746.9198)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>TFPR0_LIST_3</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>(1678.0748, 2068.8449, 3746.9198)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>FPR1_LIST_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>FPR1_LIST_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>FPR1_LIST_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>TFPR1_LIST_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>TFPR1_LIST_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>TFPR1_LIST_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Modifications_Count</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>|SIM(A*,B)|</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>8</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>|DIFF(A*,B)|</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
